--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_228_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_228_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>15</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>16</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1531,16 +1531,16 @@
         <v>33</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
         <v>13</v>
@@ -1923,10 +1923,10 @@
         <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>15</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2511,10 +2511,10 @@
         <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>15</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3102,13 +3102,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>6</v>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>3</v>
@@ -3827,16 +3827,16 @@
         <v>131</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
         <v>40</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4684,16 +4684,16 @@
         <v>19</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
         <v>3</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>3</v>
@@ -5275,13 +5275,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X40" t="n">
         <v>2</v>
@@ -5468,10 +5468,10 @@
         <v>13</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>1</v>
@@ -5664,10 +5664,10 @@
         <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>4</v>
@@ -6784,16 +6784,16 @@
         <v>95</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X48" t="n">
         <v>32</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_228_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_228_EL.xlsx
@@ -674,10 +674,10 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>82.05</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2327,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3503,14 +3503,14 @@
         <v>1</v>
       </c>
       <c r="X28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>4</v>
       </c>
       <c r="X30" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4696,14 +4696,14 @@
         <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5284,14 +5284,14 @@
         <v>2</v>
       </c>
       <c r="X40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,10 +5676,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6264,14 +6264,14 @@
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6460,10 +6460,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>8</v>
       </c>
       <c r="X48" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="Y48" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="AA48" t="n">
